--- a/Table/Excel/Text_UI.xlsx
+++ b/Table/Excel/Text_UI.xlsx
@@ -166,8 +166,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_UI" displayName="Text_UI" ref="B2:E41" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B2:E41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_UI" displayName="Text_UI" ref="B2:E42" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:E42"/>
   <tableColumns count="4">
     <tableColumn id="1" name="DataId"/>
     <tableColumn id="2" name="Key" dataDxfId="3"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E41"/>
+  <dimension ref="B2:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="3.125" customWidth="1" style="3" min="1" max="1"/>
@@ -584,12 +584,12 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>사담 나누기</t>
+          <t>사담</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Small talk</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>증거 구하기</t>
+          <t>조사할 것이...</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>Find evidence</t>
+          <t>About the case...</t>
         </is>
       </c>
     </row>
@@ -624,17 +624,17 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>대화 끝내기</t>
+          <t>끝</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>End conversation</t>
+          <t>Bye</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
+      <c r="B9" s="0" t="n">
         <v>6</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="0" t="n">
         <v>7</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="0" t="n">
         <v>8</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="0" t="n">
         <v>9</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="0" t="n">
         <v>10</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>11</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
+      <c r="B15" s="0" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
+      <c r="B16" s="0" t="n">
         <v>13</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
+      <c r="B17" s="0" t="n">
         <v>14</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
+      <c r="B18" s="0" t="n">
         <v>15</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
+      <c r="B19" s="0" t="n">
         <v>16</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
+      <c r="B20" s="0" t="n">
         <v>17</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
+      <c r="B21" s="0" t="n">
         <v>18</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
+      <c r="B22" s="0" t="n">
         <v>19</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
+      <c r="B23" s="0" t="n">
         <v>20</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
+      <c r="B24" s="0" t="n">
         <v>21</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
+      <c r="B25" s="0" t="n">
         <v>22</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
+      <c r="B26" s="0" t="n">
         <v>23</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
+      <c r="B27" s="0" t="n">
         <v>24</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
+      <c r="B28" s="0" t="n">
         <v>25</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
+      <c r="B29" s="0" t="n">
         <v>26</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
+      <c r="B30" s="0" t="n">
         <v>27</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
+      <c r="B31" s="0" t="n">
         <v>28</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
+      <c r="B32" s="0" t="n">
         <v>29</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
+      <c r="B33" s="0" t="n">
         <v>30</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
+      <c r="B34" s="0" t="n">
         <v>31</v>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
+      <c r="B35" s="0" t="n">
         <v>32</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
+      <c r="B36" s="0" t="n">
         <v>33</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
+      <c r="B37" s="0" t="n">
         <v>34</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
+      <c r="B38" s="0" t="n">
         <v>35</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
+      <c r="B39" s="0" t="n">
         <v>36</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
+      <c r="B40" s="0" t="n">
         <v>37</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>38</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1290,6 +1290,26 @@
       <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Notes saved</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>39</v>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>ui.talk_menu.request</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>부탁할 것이 있는지</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Need any help?</t>
         </is>
       </c>
     </row>

--- a/Table/Excel/Text_UI.xlsx
+++ b/Table/Excel/Text_UI.xlsx
@@ -166,8 +166,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_UI" displayName="Text_UI" ref="B2:E42" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B2:E42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_UI" displayName="Text_UI" ref="B2:E44" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:E44"/>
   <tableColumns count="4">
     <tableColumn id="1" name="DataId"/>
     <tableColumn id="2" name="Key" dataDxfId="3"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E42"/>
+  <dimension ref="B2:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="3.125" customWidth="1" style="3" min="1" max="1"/>
@@ -1294,7 +1294,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>39</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1310,6 +1310,46 @@
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Need any help?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>ui.title.quit</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>종료</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Quit</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>41</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>ui.title.quit.confirm</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>게임을 종료할까요?</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Quit the game?</t>
         </is>
       </c>
     </row>

--- a/Table/Excel/Text_UI.xlsx
+++ b/Table/Excel/Text_UI.xlsx
@@ -166,8 +166,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_UI" displayName="Text_UI" ref="B2:E43" headerRowCount="1" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="B2:E43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_UI" displayName="Text_UI" ref="B2:E45" headerRowCount="1" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="B2:E45"/>
   <tableColumns count="4">
     <tableColumn id="1" name="DataId"/>
     <tableColumn id="2" name="Key" dataDxfId="2"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E44"/>
+  <dimension ref="B2:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col width="3.125" customWidth="1" style="3" min="1" max="1"/>
@@ -1334,10 +1334,36 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="0" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
+      <c r="B44" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>ui.go_up</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>올라가기</t>
+        </is>
+      </c>
       <c r="E44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>ui.go_down</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>내려가기</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
